--- a/sample_data/omnia_jet/JET_Input.xlsx
+++ b/sample_data/omnia_jet/JET_Input.xlsx
@@ -415,13 +415,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H14"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>G/L</t>
+          <t>Account Number</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -446,29 +446,39 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
+          <t>Closing Balance</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Debit</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Credit</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Closing Balance</t>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Local Currency</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Closing Date</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>10100000</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ZeroBal Fund Trf</t>
+          <t>Cash and Bank - Current Account</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -478,31 +488,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Control Account</t>
+          <t>Cash and cash equivalents</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>45200000</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>38750000</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>12500000</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>18950000</v>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>10200000</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Zero Bal Others</t>
+          <t>Short-term Investments</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -512,167 +532,217 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Control Account</t>
+          <t>Cash and cash equivalents</t>
         </is>
       </c>
       <c r="E3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="F3" t="n">
+        <v>10000000</v>
+      </c>
+      <c r="G3" t="n">
         <v>0</v>
-      </c>
-      <c r="F3" t="n">
-        <v>160413148</v>
-      </c>
-      <c r="G3" t="n">
-        <v>160413148</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
       </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1000001</t>
+          <t>11401000</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Eq.Sh.Cap-Rs.10</t>
+          <t>Trade Receivables - Domestic</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Liabilities</t>
+          <t>Assets</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Share Capital</t>
+          <t>Trade Receivables</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>-1172000000</v>
+        <v>148500000</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>162000000</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>42500000</v>
       </c>
       <c r="H4" t="n">
-        <v>-1172000000</v>
+        <v>29000000</v>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1081001</t>
+          <t>11402000</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Preference Share Cap</t>
+          <t>Trade Receivables - Export</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Liabilities</t>
+          <t>Assets</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Preference Share Capital</t>
+          <t>Trade Receivables</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>32000000</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>28500000</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>8200000</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>11700000</v>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>1130001</t>
+          <t>11500000</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Share Premium - Equi</t>
+          <t>Prepaid Expenses</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Liabilities</t>
+          <t>Assets</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Securities Premium</t>
+          <t>Other current assets</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>3800000</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>4200000</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>2100000</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>1700000</v>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1160001</t>
+          <t>11600000</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Profit And Loss A/c</t>
+          <t>Security Deposits</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Liabilities</t>
+          <t>Assets</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Retained Earnings</t>
+          <t>Other non-current assets</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>-32516305</v>
+        <v>5000000</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>5000000</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>-32516305</v>
+        <v>0</v>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>11401000</t>
+          <t>12100000</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Trade Receivables Dom</t>
+          <t>Inventories - Raw Materials</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -682,167 +752,217 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Trade Receivables</t>
+          <t>Inventories</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>15000000</v>
+        <v>62000000</v>
       </c>
       <c r="F8" t="n">
-        <v>2138201</v>
+        <v>58000000</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>38000000</v>
       </c>
       <c r="H8" t="n">
-        <v>17138201</v>
+        <v>42000000</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>11202200</t>
+          <t>12200000</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Cost of Sales Material</t>
+          <t>Inventories - Finished Goods</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Assets</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>COST OF SALES AND SERVICES</t>
+          <t>Inventories</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>28000000</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>31500000</v>
       </c>
       <c r="G9" t="n">
-        <v>1812035</v>
+        <v>18500000</v>
       </c>
       <c r="H9" t="n">
-        <v>-1812035</v>
+        <v>15000000</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>21302630</t>
+          <t>51001000</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Output GST Clearing</t>
+          <t>Property, Plant &amp; Machinery</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Liabilities</t>
+          <t>Assets</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Other Payables</t>
+          <t>Property, plant and equipment</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>540000000</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>558000000</v>
       </c>
       <c r="G10" t="n">
-        <v>326166</v>
+        <v>22000000</v>
       </c>
       <c r="H10" t="n">
-        <v>-326166</v>
+        <v>4000000</v>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>41001400</t>
+          <t>51002000</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Sales - Domestic</t>
+          <t>Accumulated Depreciation</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Assets</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NET SALES REVENUE</t>
+          <t>Property, plant and equipment</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>-4295306840</v>
+        <v>-180000000</v>
       </c>
       <c r="F11" t="n">
-        <v>500000</v>
+        <v>-201000000</v>
       </c>
       <c r="G11" t="n">
-        <v>1049132300</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>-5343939140</v>
+        <v>21000000</v>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>51001000</t>
+          <t>20100000</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Plant &amp; Machinery</t>
+          <t>Short-Term Borrowings</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Assets</t>
+          <t>Liabilities</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Property, plant and equipment</t>
+          <t>Borrowings</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5484823145</v>
+        <v>-80000000</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-75000000</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>25000000</v>
       </c>
       <c r="H12" t="n">
-        <v>5484823145</v>
+        <v>20000000</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>3500001</t>
+          <t>20200000</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Trade Payables - Dom</t>
+          <t>Long-Term Loans</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -852,54 +972,646 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Trade Payables</t>
+          <t>Borrowings</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>-3164019</v>
+        <v>-250000000</v>
       </c>
       <c r="F13" t="n">
-        <v>55410257</v>
+        <v>-230000000</v>
       </c>
       <c r="G13" t="n">
-        <v>103457461</v>
+        <v>20000000</v>
       </c>
       <c r="H13" t="n">
-        <v>-51211223</v>
+        <v>0</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
+          <t>21100000</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Trade Payables - Domestic</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Trade Payables</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>-42000000</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-48000000</v>
+      </c>
+      <c r="G14" t="n">
+        <v>35000000</v>
+      </c>
+      <c r="H14" t="n">
+        <v>41000000</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>21200000</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Accrued Liabilities</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Other current liabilities</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>-18000000</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-21000000</v>
+      </c>
+      <c r="G15" t="n">
+        <v>9000000</v>
+      </c>
+      <c r="H15" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>21302630</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Output GST Clearing</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Other Payables</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-2500000</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>2500000</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>1000001</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Equity Share Capital - Rs.10</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Share Capital</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>-117200000</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-117200000</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>1160001</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>-85000000</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-110000000</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>25000000</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>41001400</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Sales Revenue - Domestic</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NET SALES REVENUE</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>-380000000</v>
+      </c>
+      <c r="F19" t="n">
+        <v>-445000000</v>
+      </c>
+      <c r="G19" t="n">
+        <v>500000</v>
+      </c>
+      <c r="H19" t="n">
+        <v>65500000</v>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>41001500</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Sales Revenue - Export</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NET SALES REVENUE</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>-42000000</v>
+      </c>
+      <c r="F20" t="n">
+        <v>-50500000</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>41301200</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Finance income</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>-3800000</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-4600000</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>800000</v>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>41301600</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Miscellaneous Income</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Other operating income (expenses), net</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>-1200000</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-1800000</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>600000</v>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>50001000</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Cost of Goods Sold</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>COST OF SALES AND SERVICES</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>215000000</v>
+      </c>
+      <c r="F23" t="n">
+        <v>248000000</v>
+      </c>
+      <c r="G23" t="n">
+        <v>33000000</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>52001000</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Employee Compensation</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>48000000</v>
+      </c>
+      <c r="F24" t="n">
+        <v>60000000</v>
+      </c>
+      <c r="G24" t="n">
+        <v>12000000</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
           <t>52002500</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Consultancy &amp; Audit Fee</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Consultancy &amp; Audit Fees</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D25" t="inlineStr">
         <is>
           <t>General and administrative expenses</t>
         </is>
       </c>
-      <c r="E14" t="n">
+      <c r="E25" t="n">
         <v>2500000</v>
       </c>
-      <c r="F14" t="n">
+      <c r="F25" t="n">
+        <v>6000000</v>
+      </c>
+      <c r="G25" t="n">
         <v>3500000</v>
       </c>
-      <c r="G14" t="n">
+      <c r="H25" t="n">
         <v>0</v>
       </c>
-      <c r="H14" t="n">
-        <v>6000000</v>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>52003000</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Depreciation Expense</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Depreciation and amortisation</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>16000000</v>
+      </c>
+      <c r="F26" t="n">
+        <v>21000000</v>
+      </c>
+      <c r="G26" t="n">
+        <v>5000000</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>52004000</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Finance Costs - Interest</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Finance costs</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>8500000</v>
+      </c>
+      <c r="F27" t="n">
+        <v>11200000</v>
+      </c>
+      <c r="G27" t="n">
+        <v>2700000</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
       </c>
     </row>
   </sheetData>
@@ -913,7 +1625,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:P33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -949,27 +1661,52 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>Fiscal Year</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Fiscal Period</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>Amount in local currency</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Currency code</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Amount in group curr</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Group Currency</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
         <is>
           <t>Text Header</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Text Details</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>User UD</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Document type description</t>
         </is>
       </c>
     </row>
@@ -981,7 +1718,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2500007294</t>
+          <t>RV2026000001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -991,54 +1728,79 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>03-Nov-25</t>
+          <t>04/05/2025</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>03-Nov-25</t>
+          <t>04/05/2025</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>03-Nov-25</t>
+          <t>04/05/2025</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>1339512.0</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Invoice Posting</t>
+          <t>5250000.0</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Normal sales batch</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>SATPUTD</t>
+          <t>63126.0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Sales Invoice - Q1 FY26</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Domestic sales billing cycle</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>JKUMAR</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Customer Invoice</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>11202200</t>
+          <t>41001400</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2500007294</t>
+          <t>RV2026000001</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1048,54 +1810,79 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>03-Nov-25</t>
+          <t>04/05/2025</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>03-Nov-25</t>
+          <t>04/05/2025</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>03-Nov-25</t>
+          <t>04/05/2025</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-1135180.0</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Invoice Posting</t>
+          <t>-5250000.0</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Normal sales batch</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>SATPUTD</t>
+          <t>-63126.0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>Sales Invoice - Q1 FY26</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Domestic sales billing cycle</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>JKUMAR</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Customer Invoice</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>21302630</t>
+          <t>11401000</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2500007294</t>
+          <t>RV2026000002</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1105,54 +1892,79 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>03-Nov-25</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>03-Nov-25</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>03-Nov-25</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>-204332.0</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>Invoice Posting</t>
+          <t>3800000.0</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Normal sales batch</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>SATPUTD</t>
+          <t>45734.0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Sales Invoice - Q1 FY26</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Standard billing run</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>PSINGH</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Customer Invoice</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>11401000</t>
+          <t>41001400</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2500007295</t>
+          <t>RV2026000002</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1162,54 +1974,79 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>03-Nov-25</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>03-Nov-25</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>03-Nov-25</t>
+          <t>05/12/2025</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>798689.0</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Invoice Posting</t>
+          <t>-3800000.0</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Standard billing</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>SATPUTD</t>
+          <t>-45734.0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Sales Invoice - Q1 FY26</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Standard billing run</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>PSINGH</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Customer Invoice</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>11202200</t>
+          <t>11402000</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2500007295</t>
+          <t>RV2026000010</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1219,54 +2056,79 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>03-Nov-25</t>
+          <t>06/18/2025</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>03-Nov-25</t>
+          <t>06/18/2025</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>03-Nov-25</t>
+          <t>06/18/2025</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>-676855.0</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Invoice Posting</t>
+          <t>8500000.0</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Standard billing</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>SATPUTD</t>
+          <t>102410.0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Export Sales Invoice</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Export batch to Middle East</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>RVERMA</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Customer Invoice</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>21302630</t>
+          <t>41001500</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2500007295</t>
+          <t>RV2026000010</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1276,270 +2138,2199 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>03-Nov-25</t>
+          <t>06/18/2025</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>03-Nov-25</t>
+          <t>06/18/2025</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>03-Nov-25</t>
+          <t>06/18/2025</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>-121834.0</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Invoice Posting</t>
+          <t>-8500000.0</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Standard billing</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>SATPUTD</t>
+          <t>-102410.0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Export Sales Invoice</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Export batch to Middle East</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>RVERMA</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Customer Invoice</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>41001400</t>
+          <t>50001000</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2000001001</t>
+          <t>RE2026000020</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>31-Dec-25</t>
+          <t>07/01/2025</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>31-Dec-25</t>
+          <t>07/01/2025</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>31-Dec-25</t>
+          <t>06/28/2025</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>500000.0</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Auditor adjustment</t>
+          <t>12000000.0</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Adjustment entry to revenue</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>SBPATIL</t>
+          <t>144480.0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>Purchase Invoice COGS</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Raw material procurement</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>ASHARMA</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Vendor Invoice</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>3500001</t>
+          <t>21100000</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2000001001</t>
+          <t>RE2026000020</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>AB</t>
+          <t>RE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>31-Dec-25</t>
+          <t>07/01/2025</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>31-Dec-25</t>
+          <t>07/01/2025</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>31-Dec-25</t>
+          <t>06/28/2025</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-500000.0</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Auditor adjustment</t>
+          <t>-12000000.0</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Adjustment entry to trade payables</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>SBPATIL</t>
+          <t>-144480.0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>Purchase Invoice COGS</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Payable to vendor - Hindustan Corp</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>ASHARMA</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Vendor Invoice</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>52001000</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2000001002</t>
+          <t>PC2026000030</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>SA</t>
+          <t>PC</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>05-Nov-25</t>
+          <t>07/31/2025</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>05-Nov-25</t>
+          <t>07/31/2025</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>05-Nov-25</t>
+          <t>07/31/2025</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>1000000.0</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>INR</t>
+          <t>4</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Fund Transfer</t>
+          <t>4000000.0</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Unusual zero balance clearing</t>
+          <t>INR</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>OCPL-PRASHAN</t>
+          <t>48160.0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>Payroll July 2025</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Monthly salary disbursement</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Payroll Posting</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
+          <t>10100000</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>PC2026000030</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>PC</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>07/31/2025</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>07/31/2025</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>07/31/2025</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>-4000000.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>-48160.0</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>Payroll July 2025</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>Bank transfer - payroll</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Payroll Posting</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>52003000</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>AF2026000040</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>AF</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>09/30/2025</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>09/30/2025</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>09/30/2025</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>5000000.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>60200.0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>Depreciation Q2 FY26</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Planned asset depreciation run</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>BATCH</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Depreciation Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>51002000</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>AF2026000040</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AF</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>09/30/2025</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>09/30/2025</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>09/30/2025</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>-5000000.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>-60200.0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>Depreciation Q2 FY26</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Accum. depreciation credit</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>BATCH</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Depreciation Run</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>20200000</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ZP2026000050</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ZP</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>10/15/2025</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>10/15/2025</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20000000.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>240800.0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>Loan Repayment Q3</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Principal repayment - HDFC Bank</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>TRAO</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>10100000</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>ZP2026000050</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ZP</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>10/15/2025</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>10/15/2025</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-20000000.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>-240800.0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Loan Repayment Q3</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Bank outflow - loan settlement</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>TRAO</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>10200000</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ZP2026000055</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ZP</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>10/31/2025</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>10/31/2025</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>10/31/2025</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>800000.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>9632.0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>Interest Income Oct</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>FD interest credited</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>BATCH</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bank Receipt</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>41301200</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ZP2026000055</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ZP</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>10/31/2025</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>10/31/2025</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>10/31/2025</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-800000.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>-9632.0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>Interest Income Oct</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Interest income recognition</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>BATCH</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bank Receipt</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>41001400</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>AB2026000099</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>500000.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>6020.0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Auditor adjustment YE</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Management override - revenue</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>MGMT</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Manual Journal</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>21200000</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>AB2026000099</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AB</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-500000.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>-6020.0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>Auditor adjustment YE</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Accrual reversal entry</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>MGMT</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Manual Journal</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>41001600</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>SA2026000101</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>600000.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>7224.0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>Post-closing misc income</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Misc income recognised late</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>RDESAI</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Manual Journal</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>11500000</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>SA2026000101</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-600000.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>-7224.0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>Post-closing misc income</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Prepaid writedown</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>RDESAI</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Manual Journal</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>52002500</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2000001002</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>SA2026000110</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
         <is>
           <t>SA</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>05-Nov-25</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>05-Nov-25</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>05-Nov-25</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>01/15/2026</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>01/15/2026</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1000000.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>12040.0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>Consultancy Fees</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>External audit consultant</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>SBPATIL</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Manual Journal</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>10100000</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>SA2026000110</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>01/15/2026</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>01/15/2026</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>01/10/2026</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
         <is>
           <t>-1000000.0</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>INR</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>Fund Transfer</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Consultancy charge</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>OCPL-PRASHAN</t>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>-12040.0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>Consultancy Fees</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Bank payment to consultant</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>SBPATIL</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Manual Journal</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>21302630</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>KR2026000120</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>02/28/2026</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>02/28/2026</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>02/28/2026</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>-2500000.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>-30100.0</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>GST Output Clearing</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Quarterly GST settlement</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>ASHARMA</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Vendor Invoice</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>10100000</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>KR2026000120</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>02/28/2026</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>02/28/2026</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>02/28/2026</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>2500000.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>30100.0</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>GST Output Clearing</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Bank receipt GST refund</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>ASHARMA</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Vendor Invoice</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>52004000</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>ZP2026000130</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>ZP</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2700000.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>32508.0</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>Interest Expense YE</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Annual interest on term loan</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>20100000</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>ZP2026000130</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ZP</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>03/31/2026</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>-2700000.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>-32508.0</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Interest Expense YE</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Short-term borrowing cost</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>SYSTEM</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Payment</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>51001000</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>AA2026000140</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>08/20/2025</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>08/20/2025</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>08/18/2025</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>22000000.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>264880.0</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Asset Addition - Machinery</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>New CNC machine unit</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>TRAO</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Asset Posting</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>21100000</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>AA2026000140</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>AA</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>08/20/2025</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>08/20/2025</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>08/18/2025</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>-22000000.0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>-264880.0</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Asset Addition - Machinery</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Vendor payable - Siemens India</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>TRAO</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Asset Posting</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>12100000</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>WA2026000150</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>11/10/2025</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>11/10/2025</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>11/10/2025</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>-42000000.0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>-505680.0</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>GI to Production</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Raw material issued to shop floor</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>BATCH</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Goods Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>50001000</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>WA2026000150</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>WA</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>11/10/2025</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>11/10/2025</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>11/10/2025</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>42000000.0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>505680.0</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>GI to Production</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>COGS - material consumed</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>BATCH</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Goods Issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>41301600</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>SA2026000200</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>03/15/2026</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>03/15/2026</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>03/15/2026</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>600000.0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>7224.0</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>Misc Income - Sunday</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Unplanned misc income entry</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>OCPL01</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Manual Journal</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>11500000</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>SA2026000200</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>SA</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>03/15/2026</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>03/15/2026</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>03/15/2026</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>-600000.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>INR</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>-7224.0</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Misc Income - Sunday</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Offset to prepaid</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>OCPL01</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Manual Journal</t>
         </is>
       </c>
     </row>
@@ -1554,7 +4345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1588,21 +4379,26 @@
           <t>Account Grouping 1</t>
         </is>
       </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Account Grouping 2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DEFAULT</t>
+          <t>JIOSAT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>10100000</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ZeroBal Fund Trf</t>
+          <t>Cash and Bank - Current Account</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1612,29 +4408,34 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Control Account</t>
+          <t>Cash and cash equivalents</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Cash &amp; Bank</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DEFAULT</t>
+          <t>JIOSAT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>10200000</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Zero Bal Others</t>
+          <t>Short-term Investments</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1644,61 +4445,71 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Control Account</t>
+          <t>Cash and cash equivalents</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>Investments</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DEFAULT</t>
+          <t>JIOSAT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1000001</t>
+          <t>11401000</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Eq.Sh.Cap-Rs.10</t>
+          <t>Trade Receivables - Domestic</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Liabilities</t>
+          <t>Assets</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Share Capital</t>
+          <t>Trade Receivables</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Equity</t>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DEFAULT</t>
+          <t>JIOSAT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11401000</t>
+          <t>11402000</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Trade Receivables Dom</t>
+          <t>Trade Receivables - Export</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1714,119 +4525,139 @@
       <c r="F5" t="inlineStr">
         <is>
           <t>Receivables</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DEFAULT</t>
+          <t>JIOSAT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>11202200</t>
+          <t>11500000</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Cost of Sales Material</t>
+          <t>Prepaid Expenses</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Expenses</t>
+          <t>Assets</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>COST OF SALES AND SERVICES</t>
+          <t>Other current assets</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>COGS</t>
+          <t>Prepayments</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DEFAULT</t>
+          <t>JIOSAT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21302630</t>
+          <t>11600000</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Output GST Clearing</t>
+          <t>Security Deposits</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Liabilities</t>
+          <t>Assets</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Other Payables</t>
+          <t>Other non-current assets</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Payables</t>
+          <t>Deposits</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Non-Current Assets</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>DEFAULT</t>
+          <t>JIOSAT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>41001400</t>
+          <t>12100000</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Sales - Domestic</t>
+          <t>Inventories - Raw Materials</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Assets</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>NET SALES REVENUE</t>
+          <t>Inventories</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revenue</t>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DEFAULT</t>
+          <t>JIOSAT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>51001000</t>
+          <t>12200000</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plant &amp; Machinery</t>
+          <t>Inventories - Finished Goods</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1836,76 +4667,683 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Property, plant and equipment</t>
+          <t>Inventories</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>PPE</t>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DEFAULT</t>
+          <t>JIOSAT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3500001</t>
+          <t>51001000</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Trade Payables - Dom</t>
+          <t>Property, Plant &amp; Machinery</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Liabilities</t>
+          <t>Assets</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Trade Payables</t>
+          <t>Property, plant and equipment</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Payables</t>
+          <t>PPE - Gross</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Non-Current Assets</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DEFAULT</t>
+          <t>JIOSAT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
+          <t>51002000</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>PPE - AccDep</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Non-Current Assets</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>JIOSAT</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>20100000</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Short-Term Borrowings</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Borrowings</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Borrowings</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>JIOSAT</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>20200000</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Long-Term Loans</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Borrowings</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Borrowings</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Non-Current Liabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>JIOSAT</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>21100000</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Trade Payables - Domestic</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Trade Payables</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>JIOSAT</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>21200000</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Accrued Liabilities</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Other current liabilities</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Accruals</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>JIOSAT</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>21302630</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Output GST Clearing</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Other Payables</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tax Payables</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>JIOSAT</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1000001</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Equity Share Capital - Rs.10</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Share Capital</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Share Capital</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>JIOSAT</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1160001</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Reserves</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>JIOSAT</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>41001400</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Sales Revenue - Domestic</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>NET SALES REVENUE</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Income Statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>JIOSAT</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>41001500</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Sales Revenue - Export</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>NET SALES REVENUE</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Income Statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>JIOSAT</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>41301200</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Interest Income</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Finance income</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Income Statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>JIOSAT</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>41301600</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Miscellaneous Income</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Other operating income (expenses), net</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Other Income</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Income Statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>JIOSAT</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>50001000</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Cost of Goods Sold</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>COST OF SALES AND SERVICES</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>COGS</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Income Statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>JIOSAT</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>52001000</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Employee Compensation</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>General and administrative expenses</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Staff Costs</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Income Statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>JIOSAT</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
           <t>52002500</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Consultancy &amp; Audit Fee</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Consultancy &amp; Audit Fees</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
         <is>
           <t>Expenses</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>General and administrative expenses</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>Admin</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Income Statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>JIOSAT</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>52003000</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Depreciation Expense</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Depreciation and amortisation</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Income Statement</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>JIOSAT</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>52004000</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Finance Costs - Interest</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Finance costs</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Finance Costs</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Income Statement</t>
         </is>
       </c>
     </row>
